--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_12_Full_159_Cau/Day_12_Ngan_Hang_Phan_05_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_12_Full_159_Cau/Day_12_Ngan_Hang_Phan_05_20_Cau.xlsx
@@ -675,7 +675,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Xác định bottleneck nằm ở CPU, khả năng song song, trạng thái hay quota của dependency.</t>
+          <t>Khi tiến trình xử lý stateless bị nghẽn CPU ở mức 95% trong khi ứng dụng có thể chạy song song và yêu cầu độ sẵn sàng cao, giải pháp kiến trúc tối ưu là mở rộng theo chiều ngang (horizontal scaling) kèm kiểm tra quota downstream.</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đếm kết nối đang mở thay vì chỉ đếm số yêu cầu đã nhận, rồi loại replica không còn healthy.</t>
+          <t>Đối với các kết nối có thời lượng dài và không đồng đều như SSE streaming, thuật toán cân bằng tải phù hợp nhất là Least-Connections (kết hợp lọc sức khỏe replica) thay vì Round-Robin máy móc.</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Phân biệt khả năng của replica local với khả năng của provider bên ngoài.</t>
+          <t>Với agent I/O-bound nghẽn concurrency và queue: (b) Tín hiệu autoscaling chính là concurrency kéo dài và độ sâu/tuổi của queue, (c) cơ chế cooldown/min/max kèm shedding khi chạm trần, (e) tôn trọng quota downstream của provider và áp dụng concurrency limit toàn cục.</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách khả năng xử lý do mình scale khỏi khả năng do dependency giới hạn.</t>
+          <t>Mở rộng 20 replica với 20 cuộc gọi đồng thời mỗi replica có thể tạo ra 400 in-flight requests, vượt xa quota 100 concurrent calls của provider, dẫn đến tình trạng hàng loạt request bị lỗi 429 Rate Limit.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_12_Full_159_Cau/Day_12_Ngan_Hang_Phan_05_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_12_Full_159_Cau/Day_12_Ngan_Hang_Phan_05_20_Cau.xlsx
@@ -624,10 +624,32 @@
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 5 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đánh giá lần lượt kênh truyền, origin, identity của token rồi mới kiểm scope của thao tác.
-Phân tích theo nguyên lý thiết kế: Đánh giá lần lượt kênh truyền, origin, identity của token rồi mới kiểm scope của thao tác.</t>
+- [1.0 điểm] Đánh giá chính xác kết quả PASS cho tầng truyền dẫn TLS và tầng kiểm soát nguồn gốc CORS.
+- [2.0 điểm] Đánh giá chính xác kết quả PASS cho tầng xác thực JWT Authentication (chữ ký, thời hạn, danh tính hợp lệ).
+- [2.0 điểm] Phân tích chính xác kết quả FAIL tại tầng Authorization Scope Enforcement, trả về mã chuẩn HTTP 403 Forbidden.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Dự đoán và Phân tích Kết quả của Từng Cơ chế Kiểm soát (Layered Security Evaluation):
+   - Cơ chế 1 (Lớp Mã hóa Kênh truyền - Transport Layer Security / TLS Termination):
+     + Đánh giá: KẾT QUẢ ĐẠT (PASS).
+     + Phân tích: Yêu cầu sử dụng giao thức HTTPS với chứng chỉ TLS hợp lệ. Quá trình bắt tay mã hóa TLS Handshake thành công, dữ liệu truyền tải giữa trình duyệt và máy chủ được mã hóa an toàn bằng thuật toán mã hóa hiện đại.
+   - Cơ chế 2 (Lớp Kiểm soát Nguồn gốc Trình duyệt - CORS / Origin Policy Enforcement):
+     + Đánh giá: KẾT QUẢ ĐẠT (PASS).
+     + Phân tích: Header `Origin` gửi từ trình duyệt nằm trong danh sách trắng (Allowlist) được máy chủ cấu hình. Máy chủ chấp thuận nguồn gốc và trả về các tiêu đề CORS hợp lệ (`Access-Control-Allow-Origin: &lt;origin&gt;`, `Access-Control-Allow-Credentials: true`).
+   - Cơ chế 3 (Lớp Xác thực Danh tính - Authentication / JWT Validation Middleware):
+     + Đánh giá: KẾT QUẢ ĐẠT (PASS).
+     + Phân tích: JWT Bearer Token có cấu trúc hợp lệ, chữ ký số (Signature) khớp với khóa công khai của Identity Provider, token chưa hết hạn (`exp`), thỏa mãn điều kiện `nbf` và định danh chính xác người dùng (`user_id`).
+   - Cơ chế 4 (Lớp Phân quyền và Phạm vi Thao tác - Authorization / Scope Enforcement):
+     + Đánh giá: KẾT QUẢ TỪ CHỐI / THẤT BẠI (FAIL / REJECTED).
+     + Phân tích: Thao tác người dùng yêu cầu là một hành động ghi/thay đổi trạng thái dữ liệu (đòi hỏi scope `write`). Tuy nhiên, JWT của người dùng chỉ chứa các phạm vi quyền khác (ví dụ: chỉ có scope `read`). Tầng phân quyền phát hiện thiếu hụt đặc quyền bắt buộc.
+2. Kết quả Tổng thể của Yêu cầu và Mã Phản hồi Trả về:
+   - Máy chủ lập tức ngắt chuỗi thực thi và từ chối yêu cầu.
+   - Mã trạng thái phản hồi HTTP: `HTTP/1.1 403 Forbidden`.
+   - Thân phản hồi JSON tiêu chuẩn: `{"error": "insufficient_scope", "required_scope": "write", "message": "Token hợp lệ nhưng không đủ quyền hạn để thực thi thao tác ghi dữ liệu này."}`.
+   - Lưu ý cốt tử: Không trả về mã 401 Unauthorized vì danh tính người dùng đã được xác thực thành công; mã 403 Forbidden là chỉ báo chuẩn mực cho lỗi thiếu quyền phân bổ (Authorization Failure).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Mô hình phòng thủ chiều sâu (Defense-in-Depth) phân tách rạch ròi giữa Xác thực (Authentication - bạn là ai) và Phân quyền (Authorization - bạn được phép làm gì). Một yêu cầu có thể hoàn hảo về mặt bảo mật mạng (TLS), an toàn trình duyệt (CORS) và danh tính hợp pháp (JWT Auth), nhưng vẫn phải bị chặn dứt khoát tại chốt chặn cuối cùng (Scope Enforcement) nếu không sở hữu phạm vi quyền hạn tương ứng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+RFC 6750 (OAuth 2.0 Bearer Token Usage) &amp; OWASP API Security Top 10 - Broken Function Level Authorization</t>
         </is>
       </c>
     </row>
@@ -706,10 +728,35 @@
       <c r="K5" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Hỏi yêu cầu có chia nhỏ được không; nếu không, replica mới không giúp yêu cầu đó dùng ít RAM hơn.
-Phân tích theo nguyên lý thiết kế: Hỏi yêu cầu có chia nhỏ được không; nếu không, replica mới không giúp yêu cầu đó dùng ít RAM hơn.</t>
+- [1.0 điểm] Lựa chọn chính xác chiều mở rộng Vertical Scaling (Scale-Up) và giải thích vì sao Horizontal Scaling không thể giải quyết được.
+- [1.5 điểm] Cấu hình định lượng hạn mức tài nguyên mới với requests &gt;= 24Gi và limits &gt;= 32Gi có biên độ đệm an toàn.
+- [1.5 điểm] Thiết kế cơ chế xử lý khi vượt trần: tiền kiểm tra payload (HTTP 413) và bảo vệ cgroup giới hạn bộ nhớ.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Lựa chọn Chiều Mở rộng (Scaling Direction Selection):
+   - Lựa chọn: Mở rộng theo Chiều Dọc (Vertical Scaling / Scale-Up).
+   - Biện minh kỹ thuật:
+     + Bối cảnh chỉ rõ: Yêu cầu đơn lẻ cần tới 20GB RAM và 'không thể chia nhỏ để chạy song song' (Monolithic Memory Footprint).
+     + Trong điều kiện này, mở rộng theo chiều ngang (Horizontal Scaling / Scale-Out thêm pods) hoàn toàn vô dụng, vì nếu mỗi pod chỉ có 4GB hay 8GB RAM thì bất kỳ pod nào tiếp nhận request cũng sẽ lập tức bị hệ điều hành tiêu diệt do tràn bộ nhớ (OOMKilled).
+     + Lưu lượng thấp càng củng cố việc nâng cấp cấu hình tài nguyên của một instance đơn lẻ (Node/Pod cấu hình RAM lớn) là giải pháp tối ưu cả về mặt kỹ thuật lẫn chi phí.
+2. Thiết lập Giới hạn Tài nguyên Mới (Resource Requests and Limits Configuration):
+   - Cấu hình Container Spec (Kubernetes / Cloud Container):
+     ```yaml
+     resources:
+       requests:
+         memory: "24Gi"
+         cpu: "4"
+       limits:
+         memory: "32Gi"
+         cpu: "8"
+     ```
+   - Dành biên độ đệm (Buffer): Request 24GB đảm bảo Kubernetes scheduler chỉ xếp pod vào các worker node có tối thiểu 24GB RAM thực tế; limit 32GB bảo vệ container khỏi crash khi xảy ra phân mảnh bộ nhớ (Memory Fragmentation) trong quá trình tính toán.
+3. Cơ chế Xử lý khi Yêu cầu Vượt Trần Tài nguyên (Handling Resource Ceiling Breach):
+   - Tiền kiểm Kích thước Yêu cầu (Pre-Admission Payload Guardrail): API Gateway kiểm tra kích thước input/context; nếu ước tính tiêu thụ &gt; 28GB RAM, từ chối ngay với `HTTP 413 Payload Too Large` hoặc `HTTP 400 Bad Request`.
+   - Bảo vệ Cgroup Memory Limit: Nếu bộ nhớ tiêu thụ chạm ngưỡng trần 32GB, cgroup sẽ kích hoạt OOMKiller trên tiến trình con của tác vụ thay vì làm sập toàn bộ máy chủ node host. Trả về mã lỗi `HTTP 507 Insufficient Storage` hoặc `HTTP 500` kèm log cảnh báo P1 cho đội ngũ SRE.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Hiểu rõ bản chất của khối lượng công việc là yếu tố tiên quyết trong kiến trúc co giãn điện toán đám mây. Đối với các tác vụ AI nguyên khối không thể phân tán bộ nhớ, mở rộng chiều dọc (Vertical Scaling) kết hợp với hạn mức cgroup chặt chẽ là giải pháp duy nhất khả thi để đảm bảo tác vụ thực thi thành công mà không gây nguy cơ đổ vỡ hạ tầng dùng chung.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Kubernetes Documentation - Managing Resources for Containers: https://kubernetes.io/docs/concepts/configuration/manage-resources-containers/ và Linux Kernel Cgroups v2 Memory Controller</t>
         </is>
       </c>
     </row>
@@ -788,10 +835,25 @@
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách giải pháp tạm thời cho trạng thái session khỏi đích đến stateless có thể thay replica.
-Phân tích theo nguyên lý thiết kế: Tách giải pháp tạm thời cho trạng thái session khỏi đích đến stateless có thể thay replica.</t>
+- [1.0 điểm] Chọn chính xác policy tạm thời: Extended Connection Draining kết hợp Sticky Sessions và Rolling Update maxUnavailable = 0.
+- [1.0 điểm] Dự đoán chính xác các rủi ro kỹ thuật: quá trình rollout bị kéo dài (starvation) và stream bị ngắt nếu vượt quá grace period.
+- [1.0 điểm] Đề xuất phương án thay thế kiến trúc bền vững: ngoại biên hóa trạng thái phiên ra Redis để đạt chuẩn stateless hoàn toàn.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Lựa chọn Chính sách Triển khai Tạm thời (Temporary Rollout Policy):
+   - Áp dụng Chính sách Kéo dài Rút cạn Kết nối (Extended Connection Draining / Deregistration Delay) kết hợp Cấu hình Khóa Phiên Dính (Sticky Sessions qua Cookie Affinity) và Chiến lược Rolling Update có kiểm soát:
+     + Thiết lập `maxUnavailable = 0` và `maxSurge = 1` trong Kubernetes Deployment.
+     + Cấu hình `terminationGracePeriodSeconds = 900` (15 phút) trên Pod, kết hợp với preStop hook gửi tín hiệu chuẩn bị dừng.
+     + Khi một replica cũ chuẩn bị thay thế: Load Balancer lập tức ngừng phân phối các kết nối mới vào replica này, nhưng VẪN DUY TRÌ các kết nối HTTP Streaming hiện tại cho đến khi stream dài hoàn tất tự nhiên hoặc chạm mốc giới hạn 15 phút.
+2. Dự đoán Lỗi Tiềm ẩn trong Giai đoạn Tạm thời:
+   - Hiện tượng Nghẽn Triển khai (Rollout Starvation / Stalling): Việc chờ đợi các stream kéo dài có thể khiến quá trình deploy phiên bản mới bị treo hàng giờ đồng hồ.
+   - Đứt gãy Trải nghiệm (Stream Disruption): Nếu stream vượt quá 15 phút grace period, tiến trình sẽ bị tiêu diệt cưỡng bức bằng `SIGKILL`, làm mất toàn bộ session trong bộ nhớ của người dùng đó.
+3. Kế hoạch Thay thế Kiến trúc Dứt điểm (Permanent Architectural Migration):
+   - Tiến hành Tách biệt và Ngoại biên hóa Hoàn toàn Trạng thái (Full State Externalization): Chuyển toàn bộ dữ liệu session từ RAM tiến trình sang Redis Cluster phân tán.
+   - Khi hoàn tất, hệ thống chuyển sang mô hình hoàn toàn Stateless, loại bỏ kết nối dính (Sticky Sessions) và cho phép các replica thay thế tức thì mà không ảnh hưởng tới tiến trình stream.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Quản lý việc chuyển đổi hệ thống từ đơn khối có trạng thái (Stateful Monolith) sang phi trạng thái đám mây (Stateless Cloud-Native) đòi hỏi các giải pháp chuyển tiếp an toàn. Connection Draining bảo vệ các tác vụ stream đang dở dang trong ngắn hạn, nhưng ngoại biên hóa trạng thái phiên sang bộ nhớ đệm phân tán mới là giải pháp căn cơ để đạt được khả năng triển khai liên tục không gián đoạn.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Kubernetes Pod Lifecycle - Termination of Pods: https://kubernetes.io/docs/concepts/workloads/pods/pod-lifecycle/#pod-termination và AWS ALB Target Group Deregistration Delay</t>
         </is>
       </c>
     </row>
@@ -876,10 +938,27 @@
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Phân biệt tín hiệu khiến mở rộng với trần quota khiến phải backpressure hoặc degrade.
-Phân tích theo nguyên lý thiết kế: Phân biệt tín hiệu khiến mở rộng với trần quota khiến phải backpressure hoặc degrade.</t>
+- [1.0 điểm] Thiết kế lại chính sách mở rộng: Đặt trần replica cứng tương ứng với 200 quota và đóng băng scale-out khi gặp lỗi 429.
+- [1.5 điểm] Xử lý quá tải bằng áp lực ngược (Backpressure): Load Shedding tại API Gateway trả về 429 kèm Retry-After.
+- [1.5 điểm] Xây dựng các phương án suy giảm duyên dáng: chuyển hướng sang mô hình fallback, tối đa hóa semantic cache và worker throttling.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế Lại Chính sách Mở rộng (Scaling Policy Redesign):
+   - Vấn đề cốt tử: Tiếp tục co giãn số lượng replica theo độ dài hàng đợi (Queue Length) trong khi nhà cung cấp hạ nguồn đã chạm trần 200 cuộc gọi sẽ gây ra hiện tượng bão lỗi 429 và lãng phí điện toán.
+   - Thiết kế chính sách co giãn có nhận thức hạn ngạch (Quota-Aware Autoscaling):
+     + Đặt Trần Số lượng Replica Tối đa Cứng (Hard Max Replicas Cap): Giả sử mỗi worker replica có concurrency xử lý là 4 cuộc gọi, thì `max_replicas = 200 / 4 = 50 replicas`.
+     + Tín hiệu co giãn: Kết hợp độ dài hàng đợi với tỷ lệ lỗi nhà cung cấp. Nếu `provider_429_rate &gt; 5%`, NGAY LẬP TỨC ĐÓNG BĂNG việc scale-out (Scale-Out Freeze), bất kể hàng đợi có tăng cao đến đâu.
+2. Cách Xử lý khi Hạn ngạch Quota bị Giới hạn (Quota Saturation Handling):
+   - Bước 1 (Áp lực ngược tại Cổng vào - Ingress Backpressure &amp; Rate Limiting):
+     Khi số lượng cuộc gọi đang hoạt động đạt ngưỡng 190/200, API Gateway lập tức kích hoạt Load Shedding: Từ chối các yêu cầu mới của người dùng với mã `HTTP 429 Too Many Requests` kèm header `Retry-After: 10`, ngăn chặn việc dồn thêm tải vào hàng đợi.
+   - Bước 2 (Hạ cấp Dịch vụ Duyên dáng - Graceful Service Degradation):
+     + Tự động định tuyến một phần yêu cầu sang Mô hình Dự phòng Nhẹ hơn (Fallback Cheaper Model) có quota riêng hoặc chạy on-premise.
+     + Tăng cường sử dụng Semantic Cache: Trả về kết quả đã được lưu đệm đối với các truy vấn có ngữ nghĩa tương đồng thay vì gọi model mới.
+   - Bước 3 (Điều tiết Tốc độ Tiêu thụ của Worker - Dynamic Worker Throttling):
+     Worker tự động tăng thời gian chờ (Exponential Backoff Polling) khi phát hiện downstream quota bị bão hòa, giải phóng áp lực cho nhà cung cấp.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Tự động co giãn (Autoscaling) trong hệ thống tích hợp AI không thể chỉ dựa vào các chỉ số nội bộ như độ dài hàng đợi hay CPU. Việc thiết lập chính sách co giãn có nhận thức về hạn ngạch đối tác bên ngoài (Downstream Quota-Aware Autoscaling) kết hợp với cơ chế hạ cấp dịch vụ giúp bảo vệ doanh nghiệp khỏi tình trạng sụp đổ dây chuyền do bão rate limit.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Book - Addressing Cascading Failures: https://sre.google/sre-book/addressing-cascading-failures/ và Kubernetes KEDA External Scalers</t>
         </is>
       </c>
     </row>
@@ -1010,10 +1089,32 @@
       <c r="K12" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đọc từng điều kiện trong bối cảnh rồi nối nó với một quyết định và phép kiểm có thể quan sát.
-Phân tích theo nguyên lý thiết kế: Đọc từng điều kiện trong bối cảnh rồi nối nó với một quyết định và phép kiểm có thể quan sát.</t>
+- [1.0 điểm] Thiết kế chính xác 3 loại probe: Startup Probe khởi tạo, Liveness kiểm tra deadlock, Readiness kiểm tra dependencies.
+- [1.5 điểm] Phân lập đúng đắn: Liveness không phụ thuộc DB; Readiness kiểm tra DB bắt buộc và bỏ qua metrics exporter tùy chọn.
+- [1.5 điểm] Dự đoán chuẩn xác hành vi orchestrator: DB lỗi chỉ gỡ traffic không restart, deadlock kích hoạt restart pod, metrics lỗi vẫn chạy.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế Ba Loại Probe Chuẩn mực (Startup, Liveness, Readiness):
+   - Startup Probe (`/health/startup`):
+     + Nhiệm vụ: Đánh giá quá trình khởi động ban đầu của ứng dụng (nạp thư viện, cấu hình).
+     + Cấu hình: Kiểm tra cổng TCP hoặc endpoint nội bộ. Trong giai đoạn này, các probe khác bị tạm dừng. Khi probe này thành công một lần, nó nhường quyền cho Liveness và Readiness.
+   - Liveness Probe (`/health/liveness`):
+     + Nhiệm vụ: Kiểm tra TIẾN TRÌNH ỨNG DỤNG CÓ CÒN SỐNG VÀ KHÔNG BỊ TREO/DEADLOCK.
+     + Thiết kế: Thực thi một tác vụ bất đồng bộ nhẹ trong tiến trình (ví dụ: event loop ping, kiểm tra vòng lặp luồng). TUYỆT ĐỐI KHÔNG kiểm tra cơ sở dữ liệu ở probe này.
+     + Nếu app bị deadlock: Probe không thể phản hồi trong thời hạn timeout -&gt; Liveness FAIL.
+   - Readiness Probe (`/health/readiness`):
+     + Nhiệm vụ: Kiểm tra TÍNH SẴN SÀNG PHỤC VỤ LƯU LƯỢNG NGƯỜI DÙNG.
+     + Thiết kế: Kiểm tra các dependency BẮT BUỘC (Cơ sở dữ liệu DB). Nếu DB ngắt kết nối -&gt; Trả về `HTTP 503 Service Unavailable`. KHÔNG kiểm tra metrics exporter (dependency tùy chọn) trong probe này; metrics exporter lỗi thì ghi log cảnh báo nhưng Readiness vẫn trả về `HTTP 200 OK` (chạy ở chế độ degraded mode).
+2. Dự đoán Cách Xử lý của Hệ thống Điều phối (Orchestrator Behavior):
+   - Tình huống 1 (Cơ sở dữ liệu DB tạm thời không khả dụng):
+     Readiness Probe THẤT BẠI, trong khi Liveness Probe VẪN ĐẠT. Bộ điều phối (Kubernetes) sẽ GỠ BỎ POD KHỎI SERVICE ENDPOINTS (ngừng định tuyến lưu lượng vào Pod), nhưng TUYỆT ĐỐI KHÔNG RESTART POD. Khi DB phục hồi, Readiness tự động PASS trở lại và Pod tiếp tục nhận lưu lượng mà không bị khởi động lại vô nghĩa.
+   - Tình huống 2 (Ứng dụng bị Deadlock):
+     Liveness Probe THẤT BẠI liên tiếp vượt quá số lần retry cho phép. Bộ điều phối lập tức PHÁT TÍN HIỆU TIÊU DIỆT VÀ KHỞI ĐỘNG LẠI POD (Restart Container) để giải phóng deadlock.
+   - Tình huống 3 (Metrics exporter bị lỗi):
+     Cả Liveness và Readiness đều ĐẠT. Bộ điều phối duy trì Pod hoạt động bình thường, phục vụ người dùng trơn tru ở chế độ degraded.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân định rạch ròi trách nhiệm giữa Liveness Probe (kiểm tra sự sống của tiến trình) và Readiness Probe (kiểm tra tính sẵn sàng phục vụ) là nguyên tắc cốt lõi trong vận hành Kubernetes. Đưa dependency bên ngoài vào Liveness probe là lỗi sai kinh điển khiến toàn bộ cụm Pod bị khởi động lại liên hoàn (Cascading Restart Storm) khi cơ sở dữ liệu gặp sự cố tạm thời.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Kubernetes Documentation - Configure Liveness, Readiness and Startup Probes: https://kubernetes.io/docs/tasks/configure-pod-container/configure-liveness-readiness-startup-probes/</t>
         </is>
       </c>
     </row>
@@ -1144,10 +1245,31 @@
       <c r="K15" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 5 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đọc từng điều kiện trong bối cảnh rồi nối nó với một quyết định và phép kiểm có thể quan sát.
-Phân tích theo nguyên lý thiết kế: Đọc từng điều kiện trong bối cảnh rồi nối nó với một quyết định và phép kiểm có thể quan sát.</t>
+- [1.0 điểm] Trình bày đầy đủ vòng đời dừng hoạt động theo thứ tự chuẩn: SIGTERM -&gt; Bật cờ shutdown -&gt; Đếm ngược Grace Period -&gt; SIGKILL.
+- [2.0 điểm] Phân tích chuẩn xác kết quả của request mới đến sau SIGTERM: Bị từ chối với HTTP 503 / Connection close và chuyển hướng an toàn.
+- [2.0 điểm] Phân tích chuẩn xác kết quả của request vượt quá grace period: Bị ngắt kết nối đột ngột bởi SIGKILL, rollback DB transaction và xử lý lỗi phía client.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Mô tả Thứ tự Dừng Hoạt động có Trật tự (Graceful Termination Lifecycle Sequence):
+   - Bước 1 (Tín hiệu Ngừng Hoạt động &amp; Gỡ bỏ Endpoint):
+     Bộ điều phối (Kubernetes) gửi tín hiệu `SIGTERM` tới tiến trình chính của ứng dụng và đồng thời loại bỏ Pod khỏi danh sách Endpoint của Service / Load Balancer.
+   - Bước 2 (Kích hoạt Chế độ Đóng &amp; Chặn Yêu cầu Mới):
+     Ứng dụng bắt được `SIGTERM`, kích hoạt cờ trạng thái `is_terminating = true`. Tầng HTTP Server / Middleware lập tức từ chối mọi yêu cầu mới đến sau thời điểm này.
+   - Bước 3 (Bắt đầu Khoảng thời gian Ân hạn - Grace Period Clock):
+     Đồng hồ đếm ngược thời gian ân hạn (`terminationGracePeriodSeconds`, ví dụ 30 giây) bắt đầu chạy. Ứng dụng duy trì hoạt động để cho phép các yêu cầu đang thực thi dở dang hoàn tất bình thường.
+   - Bước 4 (Cưỡng bức Tiêu diệt sau Hết hạn Ân hạn):
+     Nếu sau 30 giây mà tiến trình vẫn chưa tự kết thúc, bộ điều phối sẽ gửi tín hiệu cưỡng bức `SIGKILL` (kill -9) để giải phóng hoàn toàn tài nguyên.
+2. Kết quả Xử lý của Từng Loại Yêu cầu:
+   - Yêu cầu Mới Đến Sau khi Nhận Tín hiệu Termination:
+     + Xử lý: Do cờ `is_terminating = true` đã bật, ứng dụng lập tức từ chối tiếp nhận và phản hồi mã lỗi `HTTP 503 Service Unavailable` kèm header `Connection: close`, hoặc đóng kết nối socket ngay lập tức.
+     + Phía Client / Ingress: Reverse Proxy nhận thấy HTTP 503 sẽ tự động chuyển hướng yêu cầu (retry / failover) sang một Pod replica khác còn khỏe mạnh, người dùng cuối không bị gián đoạn.
+   - Yêu cầu Đang Chạy Vượt Quá Thời hạn Grace Period:
+     + Xử lý: Khi hết thời gian ân hạn 30 giây, tín hiệu `SIGKILL` được phát ra tiêu diệt ngay lập tức tiến trình container.
+     + Kết quả: Kết nối TCP bị đứt gãy đột ngột (Abrupt Connection Reset / Socket Closed). Bất kỳ transaction nào đang thực hiện dở dang trong database sẽ được hệ quản trị CSDL tự động rollback.
+     + Phía Client: Trình duyệt/Client nhận lỗi `HTTP 502 Bad Gateway` hoặc lỗi mạng; client có trách nhiệm thực hiện thử lại có kiểm soát (Idempotent Retry) với request ID tương ứng.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Quy trình dừng hoạt động có trật tự (Graceful Termination) là cơ chế bảo vệ tính toàn vẹn dữ liệu và độ tin cậy của dịch vụ phân tán. Việc từ chối dứt khoát các yêu cầu mới đến muộn và cưỡng bức tiêu diệt các tác vụ chạy quá hạn bảo đảm tiến trình triển khai phần mềm mới diễn ra đúng tiến độ mà không để lại các tiến trình thây ma (zombie processes) ngốn tài nguyên.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Kubernetes Documentation - Pod Lifecycle &amp; Termination of Pods: https://kubernetes.io/docs/concepts/workloads/pods/pod-lifecycle/ và UNIX Signals Guide</t>
         </is>
       </c>
     </row>
@@ -1230,10 +1352,30 @@
       <c r="K17" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 5 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đọc từng điều kiện trong bối cảnh rồi nối nó với một quyết định và phép kiểm có thể quan sát.
-Phân tích theo nguyên lý thiết kế: Đọc từng điều kiện trong bối cảnh rồi nối nó với một quyết định và phép kiểm có thể quan sát.</t>
+- [1.0 điểm] Lựa chọn chính xác chiến lược Blue-Green Deployment và biện minh thuyết phục dựa trên 3 điều kiện: tài nguyên đủ, schema tương thích, rủi ro cao.
+- [2.0 điểm] Thiết kế thứ tự 3 cổng kiểm duyệt chi tiết: Smoke test nội bộ -&gt; Canary traffic shift 5% -&gt; Full cutover 100% kèm chỉ số giám sát.
+- [2.0 điểm] Xây dựng kế hoạch Rollback tức thì (&lt; 1s) tại tầng định tuyến mạng và bảo đảm an toàn dữ liệu nhờ schema tương thích ngược.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Lựa chọn Chiến lược Triển khai Tối ưu: Blue-Green Deployment (kết hợp Canary Gate):
+   - Lựa chọn: Áp dụng chiến lược Triển khai Xanh-Xanh lam (Blue-Green Deployment) kết hợp giai đoạn thử nghiệm lưu lượng nhỏ (Canary Phase).
+   - Biện minh dựa trên các điều kiện ràng buộc của bối cảnh:
+     + Tài nguyên dồi dào: Hệ thống có đủ năng lực tính toán để chạy song song 100% hai cụm môi trường (Blue: Phiên bản cũ đang chạy; Green: Phiên bản mới hoàn chỉnh).
+     + Cơ sở dữ liệu tương thích ngược: Lược đồ CSDL tuân thủ mẫu thiết kế Mở rộng/Thu hẹp (Expand and Contract Pattern), bảo đảm cả hai phiên bản Blue và Green đều đọc/ghi an toàn trên cùng một database mà không xung đột.
+     + Rủi ro phát hành cao: Blue-Green cho phép chạy toàn bộ các bài kiểm thử xác thực trên môi trường Green trước khi mở lưu lượng, và cung cấp khả năng Rollback tức thì (dưới 1 giây) chỉ bằng cách đổi cổng định tuyến nếu phát sinh sự cố nghiêm trọng.
+2. Thứ tự Các Cổng Kiểm duyệt (Verification Gates Pipeline):
+   - Cổng 1 (Staging &amp; Internal Smoke Gate - Green Environment Isolation):
+     Triển khai phiên bản mới lên cụm Green. Đội ngũ kiểm thử gửi các yêu cầu nội bộ có gắn HTTP Header đặc biệt (`X-Target-Env: green`) để xác thực các luồng nghiệp vụ cốt lõi, kiểm tra kết nối CSDL và tải mô hình.
+   - Cổng 2 (Canary Traffic Shift Gate - 5% Production Traffic):
+     Định tuyến 5% lưu lượng người dùng thực sang cụm Green trong vòng 30 phút. Hệ thống giám sát tự động đánh giá: Tỷ lệ lỗi HTTP 5xx phải &lt; 0.1%, độ trễ P99 không tăng quá 5% so với Blue, và không có cảnh báo ngoại lệ nghiêm trọng.
+   - Cổng 3 (Full Traffic Cutover Gate - 100% Traffic Shift):
+     Khi Cổng 2 đạt chuẩn, chuyển toàn bộ 100% lưu lượng người dùng sang Green. Cụm Blue được đưa về trạng thái chờ (Standby) và giữ nguyên vẹn trong 24 giờ.
+3. Kế hoạch và Quy trình Rollback Tức thì (Instant Rollback Plan):
+   - Nếu tại bất kỳ thời điểm nào sau cutover, hệ thống giám sát phát hiện tỷ lệ lỗi tăng đột biến hoặc vi phạm SLO: Kỹ sư hoặc hệ thống tự động kích hoạt Rollback chỉ bằng 1 lệnh chuyển đổi định tuyến tại API Gateway / DNS trỏ ngược lại 100% về cụm Blue.
+   - Thời gian khôi phục diễn ra tức thì (&lt; 1 giây) mà không cần phải chờ đợi quá trình build hay redeploy container.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Chiến lược Blue-Green Deployment là tiêu chuẩn vàng cho các bản phát hành có độ rủi ro cao khi tài nguyên hạ tầng cho phép. Nhờ việc duy trì hai môi trường giống hệt nhau và cơ sở dữ liệu tương thích ngược, kỹ sư có thể triệt tiêu hoàn toàn thời gian chết (Zero Downtime) và sở hữu một nút bấm hoàn tác khẩn cấp (Emergency Rollback Switch) tức thời khi có sự cố phát sinh.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Martin Fowler - BlueGreenDeployment: https://martinfowler.com/bliki/BlueGreenDeployment.html và AWS Whitepaper - Overview of Deployment Methodologies</t>
         </is>
       </c>
     </row>
@@ -1316,10 +1458,33 @@
       <c r="K19" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 5 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đọc từng điều kiện trong bối cảnh rồi nối nó với một quyết định và phép kiểm có thể quan sát.
-Phân tích theo nguyên lý thiết kế: Đọc từng điều kiện trong bối cảnh rồi nối nó với một quyết định và phép kiểm có thể quan sát.</t>
+- [1.0 điểm] Mô tả chính xác và đầy đủ vòng đời chuyển trạng thái: CLOSED -&gt; OPEN -&gt; HALF-OPEN -&gt; CLOSED.
+- [2.0 điểm] Phân tích chuẩn xác hành vi fail-fast của các cuộc gọi trong trạng thái OPEN (chặn tại chỗ, không gọi dependency, phản hồi &lt; 1ms).
+- [2.0 điểm] Phân tích chuẩn xác hành vi của cuộc gọi probe trong HALF-OPEN và sự phục hồi thông suốt cho các cuộc gọi kế tiếp khi trở về CLOSED.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Theo dõi Chuyển đổi Trạng thái của Circuit Breaker (State Machine Transitions):
+   - Bước 1 (CLOSED -&gt; OPEN):
+     Ở trạng thái `CLOSED` ban đầu, mọi yêu cầu đều được chuyển tiếp tới dependency. Khi số lượng lỗi liên tiếp hoặc tỷ lệ lỗi vượt ngưỡng quy định (`failure_threshold`, ví dụ 5 lỗi 5xx trong 10s), Circuit Breaker lập tức chuyển trạng thái sang `OPEN`.
+   - Bước 2 (Duy trì Trạng thái OPEN):
+     Breaker giữ trạng thái `OPEN` trong suốt thời gian làm mát (`cooldown_duration`, ví dụ 30 giây). Bộ đếm thời gian bắt đầu chạy.
+   - Bước 3 (OPEN -&gt; HALF-OPEN):
+     Khi hết thời gian cooldown 30 giây, Circuit Breaker tự động chuyển dịch trạng thái sang `HALF-OPEN` để thăm dò khả năng phục hồi của dependency.
+   - Bước 4 (HALF-OPEN -&gt; CLOSED):
+     Ở trạng thái `HALF-OPEN`, một yêu cầu thăm dò (Trial Probe) được gửi đi và THÀNH CÔNG (nhận HTTP 200). Circuit Breaker ghi nhận tín hiệu lành mạnh, lập tức chuyển trạng thái trở lại `CLOSED` và reset toàn bộ bộ đếm lỗi về 0.
+2. Phân loại Trạng thái Thực thi hay Bị chặn của Từng Cuộc gọi (Invocation Flow):
+   - Các cuộc gọi đến trong giai đoạn trạng thái OPEN:
+     + Trạng thái: BỊ CHẶN HOÀN TOÀN TẠI CHỖ (Fail Fast / Blocked).
+     + Hành vi: Circuit Breaker không gửi bất kỳ gói tin mạng nào tới dependency, trả về ngay lập tức lỗi `CircuitBreakerOpenException` hoặc mã phản hồi `HTTP 503 Service Unavailable` chỉ trong &lt; 1ms. Điều này bảo vệ dependency khỏi nguy cơ sụp đổ hoàn toàn và giải phóng tài nguyên cho ứng dụng gọi.
+   - Cuộc gọi Thăm dò (Probe Call) trong giai đoạn HALF-OPEN:
+     + Trạng thái: ĐƯỢC PHÉP THỰC THI (Allowed / Executed).
+     + Hành vi: Breaker mở cửa cho DUY NHẤT một yêu cầu này đi qua tới dependency để kiểm tra sức khỏe thực tế của dịch vụ hạ nguồn. Các yêu cầu khác đến đồng thời trong khoảnh khắc này tiếp tục bị giữ lại hoặc chặn.
+   - Các cuộc gọi tiếp theo sau khi Probe thành công:
+     + Trạng thái: ĐƯỢC PHÉP THỰC THI BÌNH THƯỜNG (Allowed / Full Flow).
+     + Hành vi: Do Breaker đã khôi phục hoàn toàn về trạng thái `CLOSED`, tất cả các yêu cầu tiếp theo đều được định tuyến thông suốt tới dependency như bình thường.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Mẫu thiết kế Ngắt mạch (Circuit Breaker Pattern) là cơ chế phòng thủ bắt buộc trong kiến trúc phân tán microservices và AI. Bằng cách fail-fast khi dịch vụ phụ thuộc bị lỗi và thăm dò thận trọng qua trạng thái Half-Open, mẫu thiết kế ngăn chặn hiện tượng lãng phí luồng xử lý (Thread Pool Exhaustion) và tạo không gian cho hệ thống hạ nguồn tự phục hồi sau sự cố quá tải.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Martin Fowler - CircuitBreaker: https://martinfowler.com/bliki/CircuitBreaker.html và Release It! (Design and Deploy Production-Ready Software) by Michael T. Nygard</t>
         </is>
       </c>
     </row>
@@ -1398,10 +1563,28 @@
       <c r="K21" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đọc từng điều kiện trong bối cảnh rồi nối nó với một quyết định và phép kiểm có thể quan sát.
-Phân tích theo nguyên lý thiết kế: Đọc từng điều kiện trong bối cảnh rồi nối nó với một quyết định và phép kiểm có thể quan sát.</t>
+- [1.0 điểm] Xác định chính xác độ trễ chờ là 5s (dựa trên header Retry-After) và bổ sung Jitter ngẫu nhiên ngăn ngừa thundering herd.
+- [1.5 điểm] Đánh giá ngân sách thời gian so với deadline 12s và lên lịch thực thi Attempt 2 an toàn tại T+5.2s.
+- [1.5 điểm] Xử lý kết thúc chuẩn xác cho cả hai trường hợp: hết số lần thử max 3 (HTTP 502/429) và hết deadline thời gian (ngắn mạch HTTP 504).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Tính toán Độ trễ (Delay) và Lên lịch Attempt Tiếp theo:
+   - Phân tích bối cảnh: Dependency trả về mã lỗi `HTTP 429 Too Many Requests` kèm tiêu đề chỉ dẫn `Retry-After: 5` giây. Yêu cầu đang sử dụng phương thức GET (có tính Idempotent an toàn), thời hạn deadline tổng thể còn lại là 12 giây, số lần thử tối đa `max_attempts = 3`. Attempt 1 vừa thất bại.
+   - Tính toán Độ trễ Thực tế (Actual Delay Calculation):
+     + Tuân thủ chỉ dẫn của server: Thời gian chờ tối thiểu bắt buộc là 5.0 giây.
+     + Bổ sung độ trôi ngẫu nhiên (Full Jitter): Thêm một khoảng ngẫu nhiên nhỏ từ 0.1 đến 0.3 giây (ví dụ: `delay = 5.2` giây) nhằm ngăn ngừa tình trạng nhiều máy khách cùng bắn lại đồng thời (Thundering Herd Problem).
+   - Đánh giá Ngân sách Thời gian (Deadline Budget Check):
+     Thời gian cần thiết để chờ và gọi lại: `5.2s + latency ước tính (0.5s) = 5.7s &lt; 12s` (vẫn còn dư ~6.3 giây). ĐỦ ĐIỀU KIỆN thực hiện Attempt 2.
+   - Lên lịch Attempt 2: Đưa vào hàng đợi ngủ (asynchronous sleep) 5.2 giây, sau đó phát Attempt 2 vào thời điểm T+5.2s.
+2. Cách Kết thúc khi Hết Thời gian hoặc Hết Số lần Thử:
+   - Kịch bản Thành công: Nếu Attempt 2 nhận `HTTP 200 OK`, dừng chuỗi retry và trả kết quả thành công ngay lập tức.
+   - Kịch bản Hết Số lần Thử (Attempts Exhaustion):
+     Nếu Attempt 2 thất bại và Attempt 3 tiếp tục nhận lỗi -&gt; Đạt ngưỡng tối đa 3 lần thử (`attempt &gt;= max_attempts`). NGỪNG RETRY NGAY LẬP TỨC. Trả về mã lỗi phản hồi cho client là `HTTP 502 Bad Gateway` hoặc chuyển tiếp `HTTP 429` kèm chi tiết lỗi.
+   - Kịch bản Hết Hạn Ngạch Thời gian (Deadline / Timeout Exhaustion):
+     Nếu tại bất kỳ thời điểm nào trước khi thử lại, thời gian còn lại đến deadline nhỏ hơn thời gian `Retry-After` (ví dụ: còn 3s mà server bắt chờ 5s): NGỪNG RETRY NGAY LẬP TỨC (Short-Circuit Deadline Cancellation). Trả về mã lỗi `HTTP 504 Gateway Timeout` kèm thông điệp rõ ràng: 'Không thể hoàn tất yêu cầu trong thời hạn deadline cam kết'.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Chiến lược thử lại thông minh (Smart Retry Strategy) yêu cầu sự phối hợp chặt chẽ giữa việc tôn trọng tín hiệu điều tiết của hạ nguồn (`Retry-After`), bổ sung Jitter ngẫu nhiên và kiểm soát chặt chẽ ngân sách thời gian toàn cục (Global Deadline Budget). Ngắn mạch sớm khi phát hiện không còn đủ thời gian giúp tiết kiệm điện toán và tránh gây tải vô ích cho hệ thống.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+RFC 6585 (Additional HTTP Status Codes - Section 4: 429 Too Many Requests) &amp; AWS Architecture Blog - Exponential Backoff And Jitter</t>
         </is>
       </c>
     </row>
